--- a/Assets/Ressources/Stats/Player_stats.xlsx
+++ b/Assets/Ressources/Stats/Player_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15F1706-A6D7-4AE7-A560-CA203FAD78D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65E6B3A-BFDE-4DD1-A069-8BBFE883D166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Crit DMG</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>Level</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Pure Water Drop</t>
   </si>
 </sst>
 </file>
@@ -371,10 +377,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -393,8 +399,14 @@
       <c r="F1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -413,2558 +425,2564 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f>A2+1</f>
+        <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3">
-        <f>INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B3:G18" si="1">INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
         <v>301</v>
       </c>
       <c r="C3">
-        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="D3">
-        <f>INT(D$2 + ($A3 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="E3">
-        <f>INT(E$2 + ($A3 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>INT(F$2 + ($A3 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f>A3+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4">
-        <f>INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>502</v>
       </c>
       <c r="C4">
-        <f>INT(C$2 + ($A4 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>202</v>
       </c>
       <c r="D4">
-        <f>INT(D$2 + ($A4 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="E4">
-        <f>INT(E$2 + ($A4 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>INT(F$2 + ($A4 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
-        <f>A4+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5">
-        <f>INT(B$2 + ($A5 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>703</v>
       </c>
       <c r="C5">
-        <f>INT(C$2 + ($A5 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>303</v>
       </c>
       <c r="D5">
-        <f>INT(D$2 + ($A5 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="E5">
-        <f>INT(E$2 + ($A5 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>INT(F$2 + ($A5 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
-        <f>A5+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6">
-        <f>INT(B$2 + ($A6 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>904</v>
       </c>
       <c r="C6">
-        <f>INT(C$2 + ($A6 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>404</v>
       </c>
       <c r="D6">
-        <f>INT(D$2 + ($A6 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>166</v>
       </c>
       <c r="E6">
-        <f>INT(E$2 + ($A6 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F6">
-        <f>INT(F$2 + ($A6 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
-        <f>A6+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7">
-        <f>INT(B$2 + ($A7 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1105</v>
       </c>
       <c r="C7">
-        <f>INT(C$2 + ($A7 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>505</v>
       </c>
       <c r="D7">
-        <f>INT(D$2 + ($A7 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>206</v>
       </c>
       <c r="E7">
-        <f>INT(E$2 + ($A7 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F7">
-        <f>INT(F$2 + ($A7 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
-        <f>A7+1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8">
-        <f>INT(B$2 + ($A8 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1306</v>
       </c>
       <c r="C8">
-        <f>INT(C$2 + ($A8 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>606</v>
       </c>
       <c r="D8">
-        <f>INT(D$2 + ($A8 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>247</v>
       </c>
       <c r="E8">
-        <f>INT(E$2 + ($A8 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F8">
-        <f>INT(F$2 + ($A8 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
-        <f>A8+1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9">
-        <f>INT(B$2 + ($A9 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1507</v>
       </c>
       <c r="C9">
-        <f>INT(C$2 + ($A9 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>707</v>
       </c>
       <c r="D9">
-        <f>INT(D$2 + ($A9 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>287</v>
       </c>
       <c r="E9">
-        <f>INT(E$2 + ($A9 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F9">
-        <f>INT(F$2 + ($A9 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
-        <f>A9+1</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10">
-        <f>INT(B$2 + ($A10 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1708</v>
       </c>
       <c r="C10">
-        <f>INT(C$2 + ($A10 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>808</v>
       </c>
       <c r="D10">
-        <f>INT(D$2 + ($A10 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>327</v>
       </c>
       <c r="E10">
-        <f>INT(E$2 + ($A10 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F10">
-        <f>INT(F$2 + ($A10 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
-        <f>A10+1</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11">
-        <f>INT(B$2 + ($A11 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1909</v>
       </c>
       <c r="C11">
-        <f>INT(C$2 + ($A11 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>909</v>
       </c>
       <c r="D11">
-        <f>INT(D$2 + ($A11 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>368</v>
       </c>
       <c r="E11">
-        <f>INT(E$2 + ($A11 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F11">
-        <f>INT(F$2 + ($A11 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
-        <f>A11+1</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12">
-        <f>INT(B$2 + ($A12 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2110</v>
       </c>
       <c r="C12">
-        <f>INT(C$2 + ($A12 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1010</v>
       </c>
       <c r="D12">
-        <f>INT(D$2 + ($A12 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>408</v>
       </c>
       <c r="E12">
-        <f>INT(E$2 + ($A12 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F12">
-        <f>INT(F$2 + ($A12 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
-        <f>A12+1</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13">
-        <f>INT(B$2 + ($A13 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B13:G28" si="2">INT(B$2 + ($A13 - 1) * ((B$101 - B$2) / 99))</f>
         <v>2311</v>
       </c>
       <c r="C13">
-        <f>INT(C$2 + ($A13 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1111</v>
       </c>
       <c r="D13">
-        <f>INT(D$2 + ($A13 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>448</v>
       </c>
       <c r="E13">
-        <f>INT(E$2 + ($A13 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F13">
-        <f>INT(F$2 + ($A13 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
-        <f>A13+1</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14">
-        <f>INT(B$2 + ($A14 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2512</v>
       </c>
       <c r="C14">
-        <f>INT(C$2 + ($A14 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1212</v>
       </c>
       <c r="D14">
-        <f>INT(D$2 + ($A14 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>489</v>
       </c>
       <c r="E14">
-        <f>INT(E$2 + ($A14 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="F14">
-        <f>INT(F$2 + ($A14 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
-        <f>A14+1</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15">
-        <f>INT(B$2 + ($A15 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2713</v>
       </c>
       <c r="C15">
-        <f>INT(C$2 + ($A15 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1313</v>
       </c>
       <c r="D15">
-        <f>INT(D$2 + ($A15 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>529</v>
       </c>
       <c r="E15">
-        <f>INT(E$2 + ($A15 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="F15">
-        <f>INT(F$2 + ($A15 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f>A15+1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16">
-        <f>INT(B$2 + ($A16 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2914</v>
       </c>
       <c r="C16">
-        <f>INT(C$2 + ($A16 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1414</v>
       </c>
       <c r="D16">
-        <f>INT(D$2 + ($A16 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>569</v>
       </c>
       <c r="E16">
-        <f>INT(E$2 + ($A16 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="F16">
-        <f>INT(F$2 + ($A16 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <f>A16+1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17">
-        <f>INT(B$2 + ($A17 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3115</v>
       </c>
       <c r="C17">
-        <f>INT(C$2 + ($A17 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1515</v>
       </c>
       <c r="D17">
-        <f>INT(D$2 + ($A17 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>610</v>
       </c>
       <c r="E17">
-        <f>INT(E$2 + ($A17 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="F17">
-        <f>INT(F$2 + ($A17 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <f>A17+1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18">
-        <f>INT(B$2 + ($A18 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3316</v>
       </c>
       <c r="C18">
-        <f>INT(C$2 + ($A18 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1616</v>
       </c>
       <c r="D18">
-        <f>INT(D$2 + ($A18 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="E18">
-        <f>INT(E$2 + ($A18 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F18">
-        <f>INT(F$2 + ($A18 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <f>A18+1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19">
-        <f>INT(B$2 + ($A19 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3517</v>
       </c>
       <c r="C19">
-        <f>INT(C$2 + ($A19 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1717</v>
       </c>
       <c r="D19">
-        <f>INT(D$2 + ($A19 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>691</v>
       </c>
       <c r="E19">
-        <f>INT(E$2 + ($A19 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F19">
-        <f>INT(F$2 + ($A19 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <f>A19+1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20">
-        <f>INT(B$2 + ($A20 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3718</v>
       </c>
       <c r="C20">
-        <f>INT(C$2 + ($A20 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1818</v>
       </c>
       <c r="D20">
-        <f>INT(D$2 + ($A20 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>731</v>
       </c>
       <c r="E20">
-        <f>INT(E$2 + ($A20 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F20">
-        <f>INT(F$2 + ($A20 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <f>A20+1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21">
-        <f>INT(B$2 + ($A21 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3919</v>
       </c>
       <c r="C21">
-        <f>INT(C$2 + ($A21 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1919</v>
       </c>
       <c r="D21">
-        <f>INT(D$2 + ($A21 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>771</v>
       </c>
       <c r="E21">
-        <f>INT(E$2 + ($A21 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F21">
-        <f>INT(F$2 + ($A21 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <f>A21+1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22">
-        <f>INT(B$2 + ($A22 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4120</v>
       </c>
       <c r="C22">
-        <f>INT(C$2 + ($A22 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2020</v>
       </c>
       <c r="D22">
-        <f>INT(D$2 + ($A22 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>812</v>
       </c>
       <c r="E22">
-        <f>INT(E$2 + ($A22 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="F22">
-        <f>INT(F$2 + ($A22 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <f>A22+1</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23">
-        <f>INT(B$2 + ($A23 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B23:G38" si="3">INT(B$2 + ($A23 - 1) * ((B$101 - B$2) / 99))</f>
         <v>4321</v>
       </c>
       <c r="C23">
-        <f>INT(C$2 + ($A23 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2121</v>
       </c>
       <c r="D23">
-        <f>INT(D$2 + ($A23 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>852</v>
       </c>
       <c r="E23">
-        <f>INT(E$2 + ($A23 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F23">
-        <f>INT(F$2 + ($A23 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <f>A23+1</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24">
-        <f>INT(B$2 + ($A24 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>4522</v>
       </c>
       <c r="C24">
-        <f>INT(C$2 + ($A24 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2222</v>
       </c>
       <c r="D24">
-        <f>INT(D$2 + ($A24 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>892</v>
       </c>
       <c r="E24">
-        <f>INT(E$2 + ($A24 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F24">
-        <f>INT(F$2 + ($A24 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f>A24+1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25">
-        <f>INT(B$2 + ($A25 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>4723</v>
       </c>
       <c r="C25">
-        <f>INT(C$2 + ($A25 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2323</v>
       </c>
       <c r="D25">
-        <f>INT(D$2 + ($A25 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>933</v>
       </c>
       <c r="E25">
-        <f>INT(E$2 + ($A25 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F25">
-        <f>INT(F$2 + ($A25 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f>A25+1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26">
-        <f>INT(B$2 + ($A26 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>4924</v>
       </c>
       <c r="C26">
-        <f>INT(C$2 + ($A26 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2424</v>
       </c>
       <c r="D26">
-        <f>INT(D$2 + ($A26 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>973</v>
       </c>
       <c r="E26">
-        <f>INT(E$2 + ($A26 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F26">
-        <f>INT(F$2 + ($A26 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <f>A26+1</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27">
-        <f>INT(B$2 + ($A27 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5125</v>
       </c>
       <c r="C27">
-        <f>INT(C$2 + ($A27 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2525</v>
       </c>
       <c r="D27">
-        <f>INT(D$2 + ($A27 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1013</v>
       </c>
       <c r="E27">
-        <f>INT(E$2 + ($A27 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F27">
-        <f>INT(F$2 + ($A27 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <f>A27+1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28">
-        <f>INT(B$2 + ($A28 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5326</v>
       </c>
       <c r="C28">
-        <f>INT(C$2 + ($A28 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2626</v>
       </c>
       <c r="D28">
-        <f>INT(D$2 + ($A28 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1054</v>
       </c>
       <c r="E28">
-        <f>INT(E$2 + ($A28 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F28">
-        <f>INT(F$2 + ($A28 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <f>A28+1</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29">
-        <f>INT(B$2 + ($A29 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5527</v>
       </c>
       <c r="C29">
-        <f>INT(C$2 + ($A29 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2727</v>
       </c>
       <c r="D29">
-        <f>INT(D$2 + ($A29 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1094</v>
       </c>
       <c r="E29">
-        <f>INT(E$2 + ($A29 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F29">
-        <f>INT(F$2 + ($A29 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <f>A29+1</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30">
-        <f>INT(B$2 + ($A30 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5728</v>
       </c>
       <c r="C30">
-        <f>INT(C$2 + ($A30 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2828</v>
       </c>
       <c r="D30">
-        <f>INT(D$2 + ($A30 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1134</v>
       </c>
       <c r="E30">
-        <f>INT(E$2 + ($A30 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="F30">
-        <f>INT(F$2 + ($A30 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <f>A30+1</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31">
-        <f>INT(B$2 + ($A31 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5929</v>
       </c>
       <c r="C31">
-        <f>INT(C$2 + ($A31 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2929</v>
       </c>
       <c r="D31">
-        <f>INT(D$2 + ($A31 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1175</v>
       </c>
       <c r="E31">
-        <f>INT(E$2 + ($A31 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="F31">
-        <f>INT(F$2 + ($A31 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <f>A31+1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32">
-        <f>INT(B$2 + ($A32 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6130</v>
       </c>
       <c r="C32">
-        <f>INT(C$2 + ($A32 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>3030</v>
       </c>
       <c r="D32">
-        <f>INT(D$2 + ($A32 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1215</v>
       </c>
       <c r="E32">
-        <f>INT(E$2 + ($A32 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="F32">
-        <f>INT(F$2 + ($A32 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <f>A32+1</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33">
-        <f>INT(B$2 + ($A33 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B33:G48" si="4">INT(B$2 + ($A33 - 1) * ((B$101 - B$2) / 99))</f>
         <v>6331</v>
       </c>
       <c r="C33">
-        <f>INT(C$2 + ($A33 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3131</v>
       </c>
       <c r="D33">
-        <f>INT(D$2 + ($A33 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1255</v>
       </c>
       <c r="E33">
-        <f>INT(E$2 + ($A33 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="F33">
-        <f>INT(F$2 + ($A33 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <f>A33+1</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34">
-        <f>INT(B$2 + ($A34 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>6532</v>
       </c>
       <c r="C34">
-        <f>INT(C$2 + ($A34 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3232</v>
       </c>
       <c r="D34">
-        <f>INT(D$2 + ($A34 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1296</v>
       </c>
       <c r="E34">
-        <f>INT(E$2 + ($A34 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="F34">
-        <f>INT(F$2 + ($A34 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <f>A34+1</f>
+        <f t="shared" ref="A35:A66" si="5">A34+1</f>
         <v>34</v>
       </c>
       <c r="B35">
-        <f>INT(B$2 + ($A35 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>6733</v>
       </c>
       <c r="C35">
-        <f>INT(C$2 + ($A35 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3333</v>
       </c>
       <c r="D35">
-        <f>INT(D$2 + ($A35 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1336</v>
       </c>
       <c r="E35">
-        <f>INT(E$2 + ($A35 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="F35">
-        <f>INT(F$2 + ($A35 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <f>A35+1</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="B36">
-        <f>INT(B$2 + ($A36 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>6934</v>
       </c>
       <c r="C36">
-        <f>INT(C$2 + ($A36 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3434</v>
       </c>
       <c r="D36">
-        <f>INT(D$2 + ($A36 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1377</v>
       </c>
       <c r="E36">
-        <f>INT(E$2 + ($A36 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="F36">
-        <f>INT(F$2 + ($A36 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <f>A36+1</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="B37">
-        <f>INT(B$2 + ($A37 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7135</v>
       </c>
       <c r="C37">
-        <f>INT(C$2 + ($A37 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3535</v>
       </c>
       <c r="D37">
-        <f>INT(D$2 + ($A37 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1417</v>
       </c>
       <c r="E37">
-        <f>INT(E$2 + ($A37 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="F37">
-        <f>INT(F$2 + ($A37 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <f>A37+1</f>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="B38">
-        <f>INT(B$2 + ($A38 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7336</v>
       </c>
       <c r="C38">
-        <f>INT(C$2 + ($A38 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3636</v>
       </c>
       <c r="D38">
-        <f>INT(D$2 + ($A38 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1457</v>
       </c>
       <c r="E38">
-        <f>INT(E$2 + ($A38 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="F38">
-        <f>INT(F$2 + ($A38 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <f>A38+1</f>
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
       <c r="B39">
-        <f>INT(B$2 + ($A39 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7537</v>
       </c>
       <c r="C39">
-        <f>INT(C$2 + ($A39 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3737</v>
       </c>
       <c r="D39">
-        <f>INT(D$2 + ($A39 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1498</v>
       </c>
       <c r="E39">
-        <f>INT(E$2 + ($A39 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="F39">
-        <f>INT(F$2 + ($A39 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <f>A39+1</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="B40">
-        <f>INT(B$2 + ($A40 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7738</v>
       </c>
       <c r="C40">
-        <f>INT(C$2 + ($A40 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3838</v>
       </c>
       <c r="D40">
-        <f>INT(D$2 + ($A40 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1538</v>
       </c>
       <c r="E40">
-        <f>INT(E$2 + ($A40 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="F40">
-        <f>INT(F$2 + ($A40 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <f>A40+1</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="B41">
-        <f>INT(B$2 + ($A41 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7939</v>
       </c>
       <c r="C41">
-        <f>INT(C$2 + ($A41 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>3939</v>
       </c>
       <c r="D41">
-        <f>INT(D$2 + ($A41 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1578</v>
       </c>
       <c r="E41">
-        <f>INT(E$2 + ($A41 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="F41">
-        <f>INT(F$2 + ($A41 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <f>A41+1</f>
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
       <c r="B42">
-        <f>INT(B$2 + ($A42 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8140</v>
       </c>
       <c r="C42">
-        <f>INT(C$2 + ($A42 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>4040</v>
       </c>
       <c r="D42">
-        <f>INT(D$2 + ($A42 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>1619</v>
       </c>
       <c r="E42">
-        <f>INT(E$2 + ($A42 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F42">
-        <f>INT(F$2 + ($A42 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <f>A42+1</f>
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
       <c r="B43">
-        <f>INT(B$2 + ($A43 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B43:G58" si="6">INT(B$2 + ($A43 - 1) * ((B$101 - B$2) / 99))</f>
         <v>8341</v>
       </c>
       <c r="C43">
-        <f>INT(C$2 + ($A43 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4141</v>
       </c>
       <c r="D43">
-        <f>INT(D$2 + ($A43 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1659</v>
       </c>
       <c r="E43">
-        <f>INT(E$2 + ($A43 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="F43">
-        <f>INT(F$2 + ($A43 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <f>A43+1</f>
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="B44">
-        <f>INT(B$2 + ($A44 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>8542</v>
       </c>
       <c r="C44">
-        <f>INT(C$2 + ($A44 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4242</v>
       </c>
       <c r="D44">
-        <f>INT(D$2 + ($A44 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1699</v>
       </c>
       <c r="E44">
-        <f>INT(E$2 + ($A44 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="F44">
-        <f>INT(F$2 + ($A44 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <f>A44+1</f>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="B45">
-        <f>INT(B$2 + ($A45 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>8743</v>
       </c>
       <c r="C45">
-        <f>INT(C$2 + ($A45 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4343</v>
       </c>
       <c r="D45">
-        <f>INT(D$2 + ($A45 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1740</v>
       </c>
       <c r="E45">
-        <f>INT(E$2 + ($A45 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="F45">
-        <f>INT(F$2 + ($A45 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <f>A45+1</f>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="B46">
-        <f>INT(B$2 + ($A46 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>8944</v>
       </c>
       <c r="C46">
-        <f>INT(C$2 + ($A46 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4444</v>
       </c>
       <c r="D46">
-        <f>INT(D$2 + ($A46 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1780</v>
       </c>
       <c r="E46">
-        <f>INT(E$2 + ($A46 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="F46">
-        <f>INT(F$2 + ($A46 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <f>A46+1</f>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="B47">
-        <f>INT(B$2 + ($A47 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>9145</v>
       </c>
       <c r="C47">
-        <f>INT(C$2 + ($A47 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4545</v>
       </c>
       <c r="D47">
-        <f>INT(D$2 + ($A47 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1820</v>
       </c>
       <c r="E47">
-        <f>INT(E$2 + ($A47 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="F47">
-        <f>INT(F$2 + ($A47 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <f>A47+1</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="B48">
-        <f>INT(B$2 + ($A48 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>9346</v>
       </c>
       <c r="C48">
-        <f>INT(C$2 + ($A48 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4646</v>
       </c>
       <c r="D48">
-        <f>INT(D$2 + ($A48 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1861</v>
       </c>
       <c r="E48">
-        <f>INT(E$2 + ($A48 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="F48">
-        <f>INT(F$2 + ($A48 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <f>A48+1</f>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="B49">
-        <f>INT(B$2 + ($A49 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>9547</v>
       </c>
       <c r="C49">
-        <f>INT(C$2 + ($A49 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4747</v>
       </c>
       <c r="D49">
-        <f>INT(D$2 + ($A49 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1901</v>
       </c>
       <c r="E49">
-        <f>INT(E$2 + ($A49 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="F49">
-        <f>INT(F$2 + ($A49 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <f>A49+1</f>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="B50">
-        <f>INT(B$2 + ($A50 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>9748</v>
       </c>
       <c r="C50">
-        <f>INT(C$2 + ($A50 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4848</v>
       </c>
       <c r="D50">
-        <f>INT(D$2 + ($A50 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1941</v>
       </c>
       <c r="E50">
-        <f>INT(E$2 + ($A50 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="F50">
-        <f>INT(F$2 + ($A50 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <f>A50+1</f>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="B51">
-        <f>INT(B$2 + ($A51 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>9949</v>
       </c>
       <c r="C51">
-        <f>INT(C$2 + ($A51 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>4949</v>
       </c>
       <c r="D51">
-        <f>INT(D$2 + ($A51 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>1982</v>
       </c>
       <c r="E51">
-        <f>INT(E$2 + ($A51 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="F51">
-        <f>INT(F$2 + ($A51 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <f>A51+1</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="B52">
-        <f>INT(B$2 + ($A52 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10150</v>
       </c>
       <c r="C52">
-        <f>INT(C$2 + ($A52 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>5050</v>
       </c>
       <c r="D52">
-        <f>INT(D$2 + ($A52 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2022</v>
       </c>
       <c r="E52">
-        <f>INT(E$2 + ($A52 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="F52">
-        <f>INT(F$2 + ($A52 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <f>A52+1</f>
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
       <c r="B53">
-        <f>INT(B$2 + ($A53 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B53:G68" si="7">INT(B$2 + ($A53 - 1) * ((B$101 - B$2) / 99))</f>
         <v>10351</v>
       </c>
       <c r="C53">
-        <f>INT(C$2 + ($A53 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5151</v>
       </c>
       <c r="D53">
-        <f>INT(D$2 + ($A53 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2063</v>
       </c>
       <c r="E53">
-        <f>INT(E$2 + ($A53 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="F53">
-        <f>INT(F$2 + ($A53 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <f>A53+1</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="B54">
-        <f>INT(B$2 + ($A54 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>10552</v>
       </c>
       <c r="C54">
-        <f>INT(C$2 + ($A54 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5252</v>
       </c>
       <c r="D54">
-        <f>INT(D$2 + ($A54 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2103</v>
       </c>
       <c r="E54">
-        <f>INT(E$2 + ($A54 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="F54">
-        <f>INT(F$2 + ($A54 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <f>A54+1</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="B55">
-        <f>INT(B$2 + ($A55 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>10753</v>
       </c>
       <c r="C55">
-        <f>INT(C$2 + ($A55 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5353</v>
       </c>
       <c r="D55">
-        <f>INT(D$2 + ($A55 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2143</v>
       </c>
       <c r="E55">
-        <f>INT(E$2 + ($A55 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="F55">
-        <f>INT(F$2 + ($A55 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <f>A55+1</f>
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="B56">
-        <f>INT(B$2 + ($A56 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>10954</v>
       </c>
       <c r="C56">
-        <f>INT(C$2 + ($A56 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5454</v>
       </c>
       <c r="D56">
-        <f>INT(D$2 + ($A56 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2184</v>
       </c>
       <c r="E56">
-        <f>INT(E$2 + ($A56 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="F56">
-        <f>INT(F$2 + ($A56 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
-        <f>A56+1</f>
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
       <c r="B57">
-        <f>INT(B$2 + ($A57 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>11155</v>
       </c>
       <c r="C57">
-        <f>INT(C$2 + ($A57 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5555</v>
       </c>
       <c r="D57">
-        <f>INT(D$2 + ($A57 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2224</v>
       </c>
       <c r="E57">
-        <f>INT(E$2 + ($A57 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="F57">
-        <f>INT(F$2 + ($A57 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <f>A57+1</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="B58">
-        <f>INT(B$2 + ($A58 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>11356</v>
       </c>
       <c r="C58">
-        <f>INT(C$2 + ($A58 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5656</v>
       </c>
       <c r="D58">
-        <f>INT(D$2 + ($A58 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2264</v>
       </c>
       <c r="E58">
-        <f>INT(E$2 + ($A58 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="F58">
-        <f>INT(F$2 + ($A58 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <f>A58+1</f>
+        <f t="shared" si="5"/>
         <v>58</v>
       </c>
       <c r="B59">
-        <f>INT(B$2 + ($A59 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>11557</v>
       </c>
       <c r="C59">
-        <f>INT(C$2 + ($A59 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5757</v>
       </c>
       <c r="D59">
-        <f>INT(D$2 + ($A59 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2305</v>
       </c>
       <c r="E59">
-        <f>INT(E$2 + ($A59 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="F59">
-        <f>INT(F$2 + ($A59 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <f>A59+1</f>
+        <f t="shared" si="5"/>
         <v>59</v>
       </c>
       <c r="B60">
-        <f>INT(B$2 + ($A60 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>11758</v>
       </c>
       <c r="C60">
-        <f>INT(C$2 + ($A60 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5858</v>
       </c>
       <c r="D60">
-        <f>INT(D$2 + ($A60 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2345</v>
       </c>
       <c r="E60">
-        <f>INT(E$2 + ($A60 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="F60">
-        <f>INT(F$2 + ($A60 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <f>A60+1</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="B61">
-        <f>INT(B$2 + ($A61 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>11959</v>
       </c>
       <c r="C61">
-        <f>INT(C$2 + ($A61 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>5959</v>
       </c>
       <c r="D61">
-        <f>INT(D$2 + ($A61 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2385</v>
       </c>
       <c r="E61">
-        <f>INT(E$2 + ($A61 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="F61">
-        <f>INT(F$2 + ($A61 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <f>A61+1</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="B62">
-        <f>INT(B$2 + ($A62 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>12160</v>
       </c>
       <c r="C62">
-        <f>INT(C$2 + ($A62 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>6060</v>
       </c>
       <c r="D62">
-        <f>INT(D$2 + ($A62 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>2426</v>
       </c>
       <c r="E62">
-        <f>INT(E$2 + ($A62 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="F62">
-        <f>INT(F$2 + ($A62 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <f>A62+1</f>
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="B63">
-        <f>INT(B$2 + ($A63 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B63:G78" si="8">INT(B$2 + ($A63 - 1) * ((B$101 - B$2) / 99))</f>
         <v>12361</v>
       </c>
       <c r="C63">
-        <f>INT(C$2 + ($A63 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6161</v>
       </c>
       <c r="D63">
-        <f>INT(D$2 + ($A63 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2466</v>
       </c>
       <c r="E63">
-        <f>INT(E$2 + ($A63 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="F63">
-        <f>INT(F$2 + ($A63 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <f>A63+1</f>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="B64">
-        <f>INT(B$2 + ($A64 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>12562</v>
       </c>
       <c r="C64">
-        <f>INT(C$2 + ($A64 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6262</v>
       </c>
       <c r="D64">
-        <f>INT(D$2 + ($A64 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2506</v>
       </c>
       <c r="E64">
-        <f>INT(E$2 + ($A64 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="F64">
-        <f>INT(F$2 + ($A64 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <f>A64+1</f>
+        <f t="shared" si="5"/>
         <v>64</v>
       </c>
       <c r="B65">
-        <f>INT(B$2 + ($A65 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>12763</v>
       </c>
       <c r="C65">
-        <f>INT(C$2 + ($A65 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6363</v>
       </c>
       <c r="D65">
-        <f>INT(D$2 + ($A65 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2547</v>
       </c>
       <c r="E65">
-        <f>INT(E$2 + ($A65 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="F65">
-        <f>INT(F$2 + ($A65 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <f>A65+1</f>
+        <f t="shared" si="5"/>
         <v>65</v>
       </c>
       <c r="B66">
-        <f>INT(B$2 + ($A66 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>12964</v>
       </c>
       <c r="C66">
-        <f>INT(C$2 + ($A66 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6464</v>
       </c>
       <c r="D66">
-        <f>INT(D$2 + ($A66 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2587</v>
       </c>
       <c r="E66">
-        <f>INT(E$2 + ($A66 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="F66">
-        <f>INT(F$2 + ($A66 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <f>A66+1</f>
+        <f t="shared" ref="A67:A101" si="9">A66+1</f>
         <v>66</v>
       </c>
       <c r="B67">
-        <f>INT(B$2 + ($A67 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>13165</v>
       </c>
       <c r="C67">
-        <f>INT(C$2 + ($A67 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6565</v>
       </c>
       <c r="D67">
-        <f>INT(D$2 + ($A67 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2627</v>
       </c>
       <c r="E67">
-        <f>INT(E$2 + ($A67 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="F67">
-        <f>INT(F$2 + ($A67 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <f>A67+1</f>
+        <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="B68">
-        <f>INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>13366</v>
       </c>
       <c r="C68">
-        <f>INT(C$2 + ($A68 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6666</v>
       </c>
       <c r="D68">
-        <f>INT(D$2 + ($A68 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2668</v>
       </c>
       <c r="E68">
-        <f>INT(E$2 + ($A68 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="F68">
-        <f>INT(F$2 + ($A68 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <f>A68+1</f>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="B69">
-        <f>INT(B$2 + ($A69 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>13567</v>
       </c>
       <c r="C69">
-        <f>INT(C$2 + ($A69 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6767</v>
       </c>
       <c r="D69">
-        <f>INT(D$2 + ($A69 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2708</v>
       </c>
       <c r="E69">
-        <f>INT(E$2 + ($A69 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="F69">
-        <f>INT(F$2 + ($A69 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <f>A69+1</f>
+        <f t="shared" si="9"/>
         <v>69</v>
       </c>
       <c r="B70">
-        <f>INT(B$2 + ($A70 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>13768</v>
       </c>
       <c r="C70">
-        <f>INT(C$2 + ($A70 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6868</v>
       </c>
       <c r="D70">
-        <f>INT(D$2 + ($A70 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2749</v>
       </c>
       <c r="E70">
-        <f>INT(E$2 + ($A70 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="F70">
-        <f>INT(F$2 + ($A70 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <f>A70+1</f>
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="B71">
-        <f>INT(B$2 + ($A71 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>13969</v>
       </c>
       <c r="C71">
-        <f>INT(C$2 + ($A71 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>6969</v>
       </c>
       <c r="D71">
-        <f>INT(D$2 + ($A71 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2789</v>
       </c>
       <c r="E71">
-        <f>INT(E$2 + ($A71 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="F71">
-        <f>INT(F$2 + ($A71 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <f>A71+1</f>
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="B72">
-        <f>INT(B$2 + ($A72 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>14170</v>
       </c>
       <c r="C72">
-        <f>INT(C$2 + ($A72 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>7070</v>
       </c>
       <c r="D72">
-        <f>INT(D$2 + ($A72 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>2829</v>
       </c>
       <c r="E72">
-        <f>INT(E$2 + ($A72 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="F72">
-        <f>INT(F$2 + ($A72 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
-        <f>A72+1</f>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="B73">
-        <f>INT(B$2 + ($A73 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B73:G88" si="10">INT(B$2 + ($A73 - 1) * ((B$101 - B$2) / 99))</f>
         <v>14371</v>
       </c>
       <c r="C73">
-        <f>INT(C$2 + ($A73 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7171</v>
       </c>
       <c r="D73">
-        <f>INT(D$2 + ($A73 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>2870</v>
       </c>
       <c r="E73">
-        <f>INT(E$2 + ($A73 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="F73">
-        <f>INT(F$2 + ($A73 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <f>A73+1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="B74">
-        <f>INT(B$2 + ($A74 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>14572</v>
       </c>
       <c r="C74">
-        <f>INT(C$2 + ($A74 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7272</v>
       </c>
       <c r="D74">
-        <f>INT(D$2 + ($A74 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>2910</v>
       </c>
       <c r="E74">
-        <f>INT(E$2 + ($A74 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="F74">
-        <f>INT(F$2 + ($A74 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <f>A74+1</f>
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="B75">
-        <f>INT(B$2 + ($A75 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>14773</v>
       </c>
       <c r="C75">
-        <f>INT(C$2 + ($A75 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7373</v>
       </c>
       <c r="D75">
-        <f>INT(D$2 + ($A75 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>2950</v>
       </c>
       <c r="E75">
-        <f>INT(E$2 + ($A75 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="F75">
-        <f>INT(F$2 + ($A75 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <f>A75+1</f>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="B76">
-        <f>INT(B$2 + ($A76 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>14974</v>
       </c>
       <c r="C76">
-        <f>INT(C$2 + ($A76 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7474</v>
       </c>
       <c r="D76">
-        <f>INT(D$2 + ($A76 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>2991</v>
       </c>
       <c r="E76">
-        <f>INT(E$2 + ($A76 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="F76">
-        <f>INT(F$2 + ($A76 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <f>A76+1</f>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="B77">
-        <f>INT(B$2 + ($A77 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>15175</v>
       </c>
       <c r="C77">
-        <f>INT(C$2 + ($A77 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7575</v>
       </c>
       <c r="D77">
-        <f>INT(D$2 + ($A77 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3031</v>
       </c>
       <c r="E77">
-        <f>INT(E$2 + ($A77 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="F77">
-        <f>INT(F$2 + ($A77 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <f>A77+1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="B78">
-        <f>INT(B$2 + ($A78 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>15376</v>
       </c>
       <c r="C78">
-        <f>INT(C$2 + ($A78 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7676</v>
       </c>
       <c r="D78">
-        <f>INT(D$2 + ($A78 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3071</v>
       </c>
       <c r="E78">
-        <f>INT(E$2 + ($A78 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="F78">
-        <f>INT(F$2 + ($A78 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <f>A78+1</f>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="B79">
-        <f>INT(B$2 + ($A79 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>15577</v>
       </c>
       <c r="C79">
-        <f>INT(C$2 + ($A79 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7777</v>
       </c>
       <c r="D79">
-        <f>INT(D$2 + ($A79 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3112</v>
       </c>
       <c r="E79">
-        <f>INT(E$2 + ($A79 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="F79">
-        <f>INT(F$2 + ($A79 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <f>A79+1</f>
+        <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B80">
-        <f>INT(B$2 + ($A80 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>15778</v>
       </c>
       <c r="C80">
-        <f>INT(C$2 + ($A80 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7878</v>
       </c>
       <c r="D80">
-        <f>INT(D$2 + ($A80 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3152</v>
       </c>
       <c r="E80">
-        <f>INT(E$2 + ($A80 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="F80">
-        <f>INT(F$2 + ($A80 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <f>A80+1</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="B81">
-        <f>INT(B$2 + ($A81 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>15979</v>
       </c>
       <c r="C81">
-        <f>INT(C$2 + ($A81 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>7979</v>
       </c>
       <c r="D81">
-        <f>INT(D$2 + ($A81 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3192</v>
       </c>
       <c r="E81">
-        <f>INT(E$2 + ($A81 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="F81">
-        <f>INT(F$2 + ($A81 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <f>A81+1</f>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="B82">
-        <f>INT(B$2 + ($A82 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>16180</v>
       </c>
       <c r="C82">
-        <f>INT(C$2 + ($A82 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>8080</v>
       </c>
       <c r="D82">
-        <f>INT(D$2 + ($A82 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3233</v>
       </c>
       <c r="E82">
-        <f>INT(E$2 + ($A82 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="F82">
-        <f>INT(F$2 + ($A82 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <f>A82+1</f>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="B83">
-        <f>INT(B$2 + ($A83 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B83:G98" si="11">INT(B$2 + ($A83 - 1) * ((B$101 - B$2) / 99))</f>
         <v>16381</v>
       </c>
       <c r="C83">
-        <f>INT(C$2 + ($A83 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8181</v>
       </c>
       <c r="D83">
-        <f>INT(D$2 + ($A83 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3273</v>
       </c>
       <c r="E83">
-        <f>INT(E$2 + ($A83 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="F83">
-        <f>INT(F$2 + ($A83 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <f>A83+1</f>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="B84">
-        <f>INT(B$2 + ($A84 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>16582</v>
       </c>
       <c r="C84">
-        <f>INT(C$2 + ($A84 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8282</v>
       </c>
       <c r="D84">
-        <f>INT(D$2 + ($A84 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3313</v>
       </c>
       <c r="E84">
-        <f>INT(E$2 + ($A84 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="F84">
-        <f>INT(F$2 + ($A84 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <f>A84+1</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="B85">
-        <f>INT(B$2 + ($A85 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>16783</v>
       </c>
       <c r="C85">
-        <f>INT(C$2 + ($A85 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8383</v>
       </c>
       <c r="D85">
-        <f>INT(D$2 + ($A85 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3354</v>
       </c>
       <c r="E85">
-        <f>INT(E$2 + ($A85 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="F85">
-        <f>INT(F$2 + ($A85 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
-        <f>A85+1</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="B86">
-        <f>INT(B$2 + ($A86 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>16984</v>
       </c>
       <c r="C86">
-        <f>INT(C$2 + ($A86 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8484</v>
       </c>
       <c r="D86">
-        <f>INT(D$2 + ($A86 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3394</v>
       </c>
       <c r="E86">
-        <f>INT(E$2 + ($A86 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="F86">
-        <f>INT(F$2 + ($A86 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <f>A86+1</f>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="B87">
-        <f>INT(B$2 + ($A87 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>17185</v>
       </c>
       <c r="C87">
-        <f>INT(C$2 + ($A87 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8585</v>
       </c>
       <c r="D87">
-        <f>INT(D$2 + ($A87 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3435</v>
       </c>
       <c r="E87">
-        <f>INT(E$2 + ($A87 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="F87">
-        <f>INT(F$2 + ($A87 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <f>A87+1</f>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="B88">
-        <f>INT(B$2 + ($A88 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>17386</v>
       </c>
       <c r="C88">
-        <f>INT(C$2 + ($A88 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8686</v>
       </c>
       <c r="D88">
-        <f>INT(D$2 + ($A88 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3475</v>
       </c>
       <c r="E88">
-        <f>INT(E$2 + ($A88 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="F88">
-        <f>INT(F$2 + ($A88 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <f>A88+1</f>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="B89">
-        <f>INT(B$2 + ($A89 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>17587</v>
       </c>
       <c r="C89">
-        <f>INT(C$2 + ($A89 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8787</v>
       </c>
       <c r="D89">
-        <f>INT(D$2 + ($A89 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3515</v>
       </c>
       <c r="E89">
-        <f>INT(E$2 + ($A89 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="F89">
-        <f>INT(F$2 + ($A89 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <f>A89+1</f>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="B90">
-        <f>INT(B$2 + ($A90 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>17788</v>
       </c>
       <c r="C90">
-        <f>INT(C$2 + ($A90 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8888</v>
       </c>
       <c r="D90">
-        <f>INT(D$2 + ($A90 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3556</v>
       </c>
       <c r="E90">
-        <f>INT(E$2 + ($A90 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="F90">
-        <f>INT(F$2 + ($A90 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <f>A90+1</f>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="B91">
-        <f>INT(B$2 + ($A91 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>17989</v>
       </c>
       <c r="C91">
-        <f>INT(C$2 + ($A91 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>8989</v>
       </c>
       <c r="D91">
-        <f>INT(D$2 + ($A91 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3596</v>
       </c>
       <c r="E91">
-        <f>INT(E$2 + ($A91 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="F91">
-        <f>INT(F$2 + ($A91 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <f>A91+1</f>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="B92">
-        <f>INT(B$2 + ($A92 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>18190</v>
       </c>
       <c r="C92">
-        <f>INT(C$2 + ($A92 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>9090</v>
       </c>
       <c r="D92">
-        <f>INT(D$2 + ($A92 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>3636</v>
       </c>
       <c r="E92">
-        <f>INT(E$2 + ($A92 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="F92">
-        <f>INT(F$2 + ($A92 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <f>A92+1</f>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="B93">
-        <f>INT(B$2 + ($A93 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B93:G100" si="12">INT(B$2 + ($A93 - 1) * ((B$101 - B$2) / 99))</f>
         <v>18391</v>
       </c>
       <c r="C93">
-        <f>INT(C$2 + ($A93 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9191</v>
       </c>
       <c r="D93">
-        <f>INT(D$2 + ($A93 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3677</v>
       </c>
       <c r="E93">
-        <f>INT(E$2 + ($A93 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
       <c r="F93">
-        <f>INT(F$2 + ($A93 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <f>A93+1</f>
+        <f t="shared" si="9"/>
         <v>93</v>
       </c>
       <c r="B94">
-        <f>INT(B$2 + ($A94 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>18592</v>
       </c>
       <c r="C94">
-        <f>INT(C$2 + ($A94 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9292</v>
       </c>
       <c r="D94">
-        <f>INT(D$2 + ($A94 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3717</v>
       </c>
       <c r="E94">
-        <f>INT(E$2 + ($A94 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="F94">
-        <f>INT(F$2 + ($A94 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <f>A94+1</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="B95">
-        <f>INT(B$2 + ($A95 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>18793</v>
       </c>
       <c r="C95">
-        <f>INT(C$2 + ($A95 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9393</v>
       </c>
       <c r="D95">
-        <f>INT(D$2 + ($A95 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3757</v>
       </c>
       <c r="E95">
-        <f>INT(E$2 + ($A95 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="F95">
-        <f>INT(F$2 + ($A95 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <f>A95+1</f>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="B96">
-        <f>INT(B$2 + ($A96 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>18994</v>
       </c>
       <c r="C96">
-        <f>INT(C$2 + ($A96 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9494</v>
       </c>
       <c r="D96">
-        <f>INT(D$2 + ($A96 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3798</v>
       </c>
       <c r="E96">
-        <f>INT(E$2 + ($A96 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="F96">
-        <f>INT(F$2 + ($A96 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <f>A96+1</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="B97">
-        <f>INT(B$2 + ($A97 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>19195</v>
       </c>
       <c r="C97">
-        <f>INT(C$2 + ($A97 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9595</v>
       </c>
       <c r="D97">
-        <f>INT(D$2 + ($A97 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3838</v>
       </c>
       <c r="E97">
-        <f>INT(E$2 + ($A97 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="F97">
-        <f>INT(F$2 + ($A97 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <f>A97+1</f>
+        <f t="shared" si="9"/>
         <v>97</v>
       </c>
       <c r="B98">
-        <f>INT(B$2 + ($A98 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>19396</v>
       </c>
       <c r="C98">
-        <f>INT(C$2 + ($A98 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9696</v>
       </c>
       <c r="D98">
-        <f>INT(D$2 + ($A98 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3878</v>
       </c>
       <c r="E98">
-        <f>INT(E$2 + ($A98 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="F98">
-        <f>INT(F$2 + ($A98 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <f>A98+1</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="B99">
-        <f>INT(B$2 + ($A99 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>19597</v>
       </c>
       <c r="C99">
-        <f>INT(C$2 + ($A99 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9797</v>
       </c>
       <c r="D99">
-        <f>INT(D$2 + ($A99 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3919</v>
       </c>
       <c r="E99">
-        <f>INT(E$2 + ($A99 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="F99">
-        <f>INT(F$2 + ($A99 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <f>A99+1</f>
+        <f t="shared" si="9"/>
         <v>99</v>
       </c>
       <c r="B100">
-        <f>INT(B$2 + ($A100 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>19798</v>
       </c>
       <c r="C100">
-        <f>INT(C$2 + ($A100 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>9898</v>
       </c>
       <c r="D100">
-        <f>INT(D$2 + ($A100 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>3959</v>
       </c>
       <c r="E100">
-        <f>INT(E$2 + ($A100 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="F100">
-        <f>INT(F$2 + ($A100 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <f>A100+1</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="B101">
@@ -2982,6 +3000,9 @@
       </c>
       <c r="F101">
         <v>50</v>
+      </c>
+      <c r="G101">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Ressources/Stats/Player_stats.xlsx
+++ b/Assets/Ressources/Stats/Player_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71D3166-73DB-4E63-9D49-94028C4E15A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B349A6C5-42A4-4A8B-830D-BFD68A250EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Crit DMG</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Pure Water Drop</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -380,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -3796,19 +3793,6 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>8</v>
-      </c>
-      <c r="G102">
-        <f>SUM(G2:G101)</f>
-        <v>6005539</v>
-      </c>
-      <c r="H102">
-        <f>SUM(H2:H101)</f>
-        <v>2824931</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
